--- a/docs/TimeLine.xlsx
+++ b/docs/TimeLine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTC-eLibrary\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6619E8B1-867B-4FF2-A171-70BB42891FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D43B83D-B6E2-468B-AA5E-867AC6B5D95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="72">
   <si>
     <t>STT</t>
   </si>
@@ -212,9 +212,6 @@
     <t>Cập nhật docs/API.md (endpoint Books)</t>
   </si>
   <si>
-    <t>Đang làm</t>
-  </si>
-  <si>
     <t>17:30-18:30</t>
   </si>
   <si>
@@ -252,9 +249,6 @@
   </si>
   <si>
     <t>Upload ảnh thống nhất</t>
-  </si>
-  <si>
-    <t>Chưa làm</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1457,7 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>44</v>
@@ -1488,7 +1482,7 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>44</v>
@@ -1513,7 +1507,7 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>48</v>
@@ -1538,7 +1532,7 @@
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>48</v>
@@ -1563,7 +1557,7 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>48</v>
@@ -1588,7 +1582,7 @@
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>51</v>
@@ -1613,7 +1607,7 @@
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>51</v>
@@ -1638,7 +1632,7 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>56</v>
@@ -1663,7 +1657,7 @@
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>56</v>
@@ -1678,20 +1672,20 @@
         <v>46098</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1703,20 +1697,20 @@
         <v>46098</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1728,20 +1722,20 @@
         <v>46098</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1753,20 +1747,20 @@
         <v>46098</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
